--- a/exercisesLifeContingencies/annuities/makeham.xlsx
+++ b/exercisesLifeContingencies/annuities/makeham.xlsx
@@ -420,16 +420,16 @@
         <v>100000</v>
       </c>
       <c r="C2">
-        <v>41.02974113839863</v>
+        <v>22.28393070392576</v>
       </c>
       <c r="D2">
-        <v>0.0004102974113839863</v>
+        <v>0.0002228393070392576</v>
       </c>
       <c r="E2">
-        <v>0.999589702588616</v>
+        <v>0.9997771606929607</v>
       </c>
       <c r="F2">
-        <v>71.66319036298292</v>
+        <v>85.56426560366678</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -437,19 +437,19 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>99958.97025886161</v>
+        <v>99977.71606929608</v>
       </c>
       <c r="C3">
-        <v>43.18377188662431</v>
+        <v>22.31446446393932</v>
       </c>
       <c r="D3">
-        <v>0.0004320149734915457</v>
+        <v>0.0002231943811206172</v>
       </c>
       <c r="E3">
-        <v>0.9995679850265085</v>
+        <v>0.9997768056188794</v>
       </c>
       <c r="F3">
-        <v>70.69240042058567</v>
+        <v>84.5832254906758</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -457,19 +457,19 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>99915.78648697498</v>
+        <v>99955.40160483214</v>
       </c>
       <c r="C4">
-        <v>45.48688584943878</v>
+        <v>22.34937651317246</v>
       </c>
       <c r="D4">
-        <v>0.0004552522424008387</v>
+        <v>0.0002235934842373943</v>
       </c>
       <c r="E4">
-        <v>0.9995447477575992</v>
+        <v>0.9997764065157626</v>
       </c>
       <c r="F4">
-        <v>69.72273769474938</v>
+        <v>83.60199658375426</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -477,19 +477,19 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>99870.29960112553</v>
+        <v>99933.05222831896</v>
       </c>
       <c r="C5">
-        <v>47.94928101381507</v>
+        <v>22.38920847730267</v>
       </c>
       <c r="D5">
-        <v>0.0004801155218850939</v>
+        <v>0.0002240420759505035</v>
       </c>
       <c r="E5">
-        <v>0.9995198844781149</v>
+        <v>0.9997759579240495</v>
       </c>
       <c r="F5">
-        <v>68.75426585457552</v>
+        <v>82.62058180425171</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -497,19 +497,19 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>99822.35032011171</v>
+        <v>99910.66301984167</v>
       </c>
       <c r="C6">
-        <v>50.58183621406519</v>
+        <v>22.43456899188494</v>
       </c>
       <c r="D6">
-        <v>0.0005067185460155832</v>
+        <v>0.0002245462927958908</v>
       </c>
       <c r="E6">
-        <v>0.9994932814539844</v>
+        <v>0.9997754537072041</v>
       </c>
       <c r="F6">
-        <v>67.78705152795786</v>
+        <v>81.63898439283155</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -517,19 +517,19 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>99771.76848389764</v>
+        <v>99888.22845084978</v>
       </c>
       <c r="C7">
-        <v>53.39615414241699</v>
+        <v>22.48614199029288</v>
       </c>
       <c r="D7">
-        <v>0.0005351829976937283</v>
+        <v>0.0002251130322263872</v>
       </c>
       <c r="E7">
-        <v>0.9994648170023063</v>
+        <v>0.9997748869677736</v>
       </c>
       <c r="F7">
-        <v>66.82116441050402</v>
+        <v>80.65720794300881</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -537,19 +537,19 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>99718.37232975522</v>
+        <v>99865.7423088595</v>
       </c>
       <c r="C8">
-        <v>56.40460671354154</v>
+        <v>22.54469601619907</v>
       </c>
       <c r="D8">
-        <v>0.0005656390632512442</v>
+        <v>0.0002257500469627916</v>
       </c>
       <c r="E8">
-        <v>0.9994343609367488</v>
+        <v>0.9997742499530372</v>
       </c>
       <c r="F8">
-        <v>65.85667737601911</v>
+        <v>79.67525643809513</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -557,19 +557,19 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>99661.96772304169</v>
+        <v>99843.1976128433</v>
       </c>
       <c r="C9">
-        <v>59.62038285531604</v>
+        <v>22.61109468680176</v>
       </c>
       <c r="D9">
-        <v>0.0005982260256088834</v>
+        <v>0.0002264660510421512</v>
       </c>
       <c r="E9">
-        <v>0.9994017739743911</v>
+        <v>0.9997735339489578</v>
       </c>
       <c r="F9">
-        <v>64.89366658833069</v>
+        <v>78.69313429188064</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -577,19 +577,19 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>99602.34734018637</v>
+        <v>99820.5865181565</v>
       </c>
       <c r="C10">
-        <v>63.05753879039505</v>
+        <v>22.68630844897002</v>
       </c>
       <c r="D10">
-        <v>0.0006330928986545414</v>
+        <v>0.0002272708390151923</v>
       </c>
       <c r="E10">
-        <v>0.9993669071013455</v>
+        <v>0.9997727291609848</v>
       </c>
       <c r="F10">
-        <v>63.93221161420586</v>
+        <v>77.71084639341203</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -597,19 +597,19 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>99539.28980139598</v>
+        <v>99797.90020970753</v>
       </c>
       <c r="C11">
-        <v>66.73105086317743</v>
+        <v>22.77142778784285</v>
       </c>
       <c r="D11">
-        <v>0.0006703991056830061</v>
+        <v>0.000228175419923593</v>
       </c>
       <c r="E11">
-        <v>0.999329600894317</v>
+        <v>0.9997718245800764</v>
       </c>
       <c r="F11">
-        <v>62.97239553708098</v>
+        <v>76.72839815625679</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -617,19 +617,19 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>99472.5587505328</v>
+        <v>99775.12878191969</v>
       </c>
       <c r="C12">
-        <v>70.65687095394316</v>
+        <v>22.86767806680746</v>
       </c>
       <c r="D12">
-        <v>0.0007103152049314776</v>
+        <v>0.0002291921678877484</v>
       </c>
       <c r="E12">
-        <v>0.9992896847950685</v>
+        <v>0.9997708078321123</v>
       </c>
       <c r="F12">
-        <v>62.01430507129317</v>
+        <v>75.745795572679</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -637,19 +637,19 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>99401.90187957886</v>
+        <v>99752.26110385288</v>
       </c>
       <c r="C13">
-        <v>74.85198450612164</v>
+        <v>22.97643619998853</v>
       </c>
       <c r="D13">
-        <v>0.0007530236654506028</v>
+        <v>0.0002303349913649333</v>
       </c>
       <c r="E13">
-        <v>0.9992469763345494</v>
+        <v>0.9997696650086351</v>
       </c>
       <c r="F13">
-        <v>61.0580306764683</v>
+        <v>74.76304527318699</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -657,19 +657,19 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>99327.04989507273</v>
+        <v>99729.2846676529</v>
       </c>
       <c r="C14">
-        <v>79.33447117322143</v>
+        <v>23.09924938315849</v>
       </c>
       <c r="D14">
-        <v>0.0007987196967697008</v>
+        <v>0.0002316195233941221</v>
       </c>
       <c r="E14">
-        <v>0.9992012803032303</v>
+        <v>0.9997683804766059</v>
       </c>
       <c r="F14">
-        <v>60.10366667168516</v>
+        <v>73.78015459195352</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -677,19 +677,19 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>99247.71542389951</v>
+        <v>99706.18541826974</v>
       </c>
       <c r="C15">
-        <v>84.12356806795022</v>
+        <v>23.23785613606873</v>
       </c>
       <c r="D15">
-        <v>0.000847612136044118</v>
+        <v>0.0002330633354248324</v>
       </c>
       <c r="E15">
-        <v>0.9991523878639559</v>
+        <v>0.9997669366645752</v>
       </c>
       <c r="F15">
-        <v>59.15131134899774</v>
+        <v>72.79713163864982</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -697,19 +697,19 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>99163.59185583156</v>
+        <v>99682.94756213368</v>
       </c>
       <c r="C16">
-        <v>89.23973556833595</v>
+        <v>23.39420994107155</v>
       </c>
       <c r="D16">
-        <v>0.0008999243966281156</v>
+        <v>0.0002346861776583165</v>
       </c>
       <c r="E16">
-        <v>0.9991000756033719</v>
+        <v>0.9997653138223417</v>
       </c>
       <c r="F16">
-        <v>58.20106708585845</v>
+        <v>71.81398537727971</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -717,19 +717,19 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>99074.35212026323</v>
+        <v>99659.5533521926</v>
       </c>
       <c r="C17">
-        <v>94.70472560042595</v>
+        <v>23.57050579692938</v>
       </c>
       <c r="D17">
-        <v>0.0009558954822683763</v>
+        <v>0.0002365102491843629</v>
       </c>
       <c r="E17">
-        <v>0.9990441045177316</v>
+        <v>0.9997634897508156</v>
       </c>
       <c r="F17">
-        <v>57.25304045594421</v>
+        <v>70.83072571264681</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -737,19 +737,19 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>98979.6473946628</v>
+        <v>99635.98284639567</v>
       </c>
       <c r="C18">
-        <v>100.5416522778493</v>
+        <v>23.76921004595136</v>
       </c>
       <c r="D18">
-        <v>0.001015781071405097</v>
+        <v>0.000238560501607088</v>
       </c>
       <c r="E18">
-        <v>0.9989842189285949</v>
+        <v>0.9997614394983929</v>
       </c>
       <c r="F18">
-        <v>56.30734233784462</v>
+        <v>69.84736358513778</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -757,19 +757,19 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>98879.10574238494</v>
+        <v>99612.21363634971</v>
       </c>
       <c r="C19">
-        <v>106.7750647299199</v>
+        <v>23.99309387628278</v>
       </c>
       <c r="D19">
-        <v>0.001079854676357073</v>
+        <v>0.0002408649803112839</v>
       </c>
       <c r="E19">
-        <v>0.9989201453236429</v>
+        <v>0.9997591350196887</v>
       </c>
       <c r="F19">
-        <v>55.36408802102768</v>
+        <v>68.86391107455717</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -777,19 +777,19 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>98772.33067765502</v>
+        <v>99588.22054247343</v>
       </c>
       <c r="C20">
-        <v>113.4310218939008</v>
+        <v>24.24527094990752</v>
       </c>
       <c r="D20">
-        <v>0.001148408882484353</v>
+        <v>0.000243455208034038</v>
       </c>
       <c r="E20">
-        <v>0.9988515911175156</v>
+        <v>0.999756544791966</v>
       </c>
       <c r="F20">
-        <v>54.42339730845264</v>
+        <v>67.88038151380417</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -797,19 +797,19 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>98658.89965576111</v>
+        <v>99563.97527152352</v>
       </c>
       <c r="C21">
-        <v>120.5371689818844</v>
+        <v>24.52923966152514</v>
       </c>
       <c r="D21">
-        <v>0.00122175667276303</v>
+        <v>0.0002463666159836508</v>
       </c>
       <c r="E21">
-        <v>0.998778243327237</v>
+        <v>0.9997536333840163</v>
       </c>
       <c r="F21">
-        <v>53.4853946151531</v>
+        <v>66.89678961324029</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -817,19 +817,19 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>98538.36248677922</v>
+        <v>99539.446031862</v>
       </c>
       <c r="C22">
-        <v>128.1228152552156</v>
+        <v>24.84893059472741</v>
       </c>
       <c r="D22">
-        <v>0.00130023284355274</v>
+        <v>0.000249639028398585</v>
       </c>
       <c r="E22">
-        <v>0.9986997671564473</v>
+        <v>0.9997503609716014</v>
       </c>
       <c r="F22">
-        <v>52.55020906206617</v>
+        <v>65.91315159665596</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -837,19 +837,19 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>98410.239671524</v>
+        <v>99514.59710126727</v>
       </c>
       <c r="C23">
-        <v>136.2190126516928</v>
+        <v>25.20875981004588</v>
       </c>
       <c r="D23">
-        <v>0.001384195517726283</v>
+        <v>0.0002533172071670364</v>
       </c>
       <c r="E23">
-        <v>0.9986158044822737</v>
+        <v>0.999746682792833</v>
       </c>
       <c r="F23">
-        <v>51.61797456433415</v>
+        <v>64.92948534980732</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -857,19 +857,19 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>98274.02065887231</v>
+        <v>99489.38834145722</v>
       </c>
       <c r="C24">
-        <v>144.8586347068926</v>
+        <v>25.61368867592734</v>
       </c>
       <c r="D24">
-        <v>0.001474027761718677</v>
+        <v>0.0002574514639492875</v>
       </c>
       <c r="E24">
-        <v>0.9985259722382813</v>
+        <v>0.9997425485360507</v>
       </c>
       <c r="F24">
-        <v>50.68882991325774</v>
+        <v>63.94581058255771</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -877,19 +877,19 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>98129.16202416542</v>
+        <v>99463.77465278129</v>
       </c>
       <c r="C25">
-        <v>154.0764550935945</v>
+        <v>26.06929103873174</v>
       </c>
       <c r="D25">
-        <v>0.001570139313486152</v>
+        <v>0.0002620983481648187</v>
       </c>
       <c r="E25">
-        <v>0.9984298606865138</v>
+        <v>0.9997379016518352</v>
       </c>
       <c r="F25">
-        <v>49.76291885102917</v>
+        <v>62.96214900572461</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -897,19 +897,19 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>97975.08556907182</v>
+        <v>99437.70536174256</v>
       </c>
       <c r="C26">
-        <v>163.9092249666821</v>
+        <v>26.58182862274045</v>
       </c>
       <c r="D26">
-        <v>0.001672968428806598</v>
+        <v>0.0002673214202403296</v>
       </c>
       <c r="E26">
-        <v>0.9983270315711934</v>
+        <v>0.9997326785797597</v>
       </c>
       <c r="F26">
-        <v>48.84039013732653</v>
+        <v>61.97852452379806</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -917,19 +917,19 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>97811.17634410513</v>
+        <v>99411.12353311981</v>
       </c>
       <c r="C27">
-        <v>174.3957481454433</v>
+        <v>27.15833565723852</v>
       </c>
       <c r="D27">
-        <v>0.001782983853827802</v>
+        <v>0.0002731921206804433</v>
       </c>
       <c r="E27">
-        <v>0.9982170161461722</v>
+        <v>0.9997268078793196</v>
       </c>
       <c r="F27">
-        <v>47.9213976068014</v>
+        <v>60.99496344476375</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -937,19 +937,19 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>97636.78059595969</v>
+        <v>99383.96519746257</v>
       </c>
       <c r="C28">
-        <v>185.5769529876072</v>
+        <v>27.80671384487818</v>
       </c>
       <c r="D28">
-        <v>0.001900686932269524</v>
+        <v>0.0002797907468234939</v>
       </c>
       <c r="E28">
-        <v>0.9980993130677305</v>
+        <v>0.9997202092531765</v>
       </c>
       <c r="F28">
-        <v>47.00610021644565</v>
+        <v>60.01149470832866</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -957,19 +957,19 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>97451.20364297208</v>
+        <v>99356.15848361769</v>
       </c>
       <c r="C29">
-        <v>197.4959596073467</v>
+        <v>28.53583891695504</v>
       </c>
       <c r="D29">
-        <v>0.002026613856211612</v>
+        <v>0.0002872075506186178</v>
       </c>
       <c r="E29">
-        <v>0.9979733861437884</v>
+        <v>0.9997127924493814</v>
       </c>
       <c r="F29">
-        <v>46.09466208177801</v>
+        <v>59.02815013391166</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -977,19 +977,19 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>97253.70768336473</v>
+        <v>99327.62264470074</v>
       </c>
       <c r="C30">
-        <v>210.1981408599101</v>
+        <v>29.35568016571148</v>
       </c>
       <c r="D30">
-        <v>0.002161338069950669</v>
+        <v>0.0002955439724025011</v>
       </c>
       <c r="E30">
-        <v>0.9978386619300493</v>
+        <v>0.9997044560275975</v>
       </c>
       <c r="F30">
-        <v>45.18725250074827</v>
+        <v>58.04496468982128</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -997,19 +997,19 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>97043.50954250482</v>
+        <v>99298.26696453503</v>
       </c>
       <c r="C31">
-        <v>223.7311752572228</v>
+        <v>30.27743450465336</v>
       </c>
       <c r="D31">
-        <v>0.002305472836998224</v>
+        <v>0.0003049140275073192</v>
       </c>
       <c r="E31">
-        <v>0.9976945271630018</v>
+        <v>0.9996950859724927</v>
       </c>
       <c r="F31">
-        <v>44.28404596421716</v>
+        <v>57.06197678509969</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1017,19 +1017,19 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>96819.77836724759</v>
+        <v>99267.98953003038</v>
       </c>
       <c r="C32">
-        <v>238.1450896860658</v>
+        <v>31.3136767854815</v>
       </c>
       <c r="D32">
-        <v>0.002459673980896304</v>
+        <v>0.0003154458646108527</v>
       </c>
       <c r="E32">
-        <v>0.9975403260191037</v>
+        <v>0.9996845541353891</v>
       </c>
       <c r="F32">
-        <v>43.38522215183383</v>
+        <v>56.07922858556097</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1037,19 +1037,19 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>96581.63327756153</v>
+        <v>99236.67585324489</v>
       </c>
       <c r="C33">
-        <v>253.4922894734195</v>
+        <v>32.47852829574072</v>
       </c>
       <c r="D33">
-        <v>0.002624642811174249</v>
+        <v>0.0003272835170715638</v>
       </c>
       <c r="E33">
-        <v>0.9973753571888258</v>
+        <v>0.9996727164829284</v>
       </c>
       <c r="F33">
-        <v>42.49096591210142</v>
+        <v>55.09676635559358</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1057,19 +1057,19 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>96328.14098808811</v>
+        <v>99204.19732494914</v>
       </c>
       <c r="C34">
-        <v>269.8275729766773</v>
+        <v>33.78784557659677</v>
       </c>
       <c r="D34">
-        <v>0.002801129246437384</v>
+        <v>0.0003405888711132121</v>
       </c>
       <c r="E34">
-        <v>0.9971988707535626</v>
+        <v>0.9996594111288868</v>
       </c>
       <c r="F34">
-        <v>41.60146722539445</v>
+        <v>54.11464082732714</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1077,19 +1077,19 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>96058.31341511144</v>
+        <v>99170.40947937254</v>
       </c>
       <c r="C35">
-        <v>287.2081274684362</v>
+        <v>35.259431935956</v>
       </c>
       <c r="D35">
-        <v>0.00298993514728163</v>
+        <v>0.000355543877665343</v>
       </c>
       <c r="E35">
-        <v>0.9970100648527184</v>
+        <v>0.9996444561223347</v>
       </c>
       <c r="F35">
-        <v>40.7169211486721</v>
+        <v>53.13290759878074</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1097,19 +1097,19 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>95771.105287643</v>
+        <v>99135.15004743657</v>
       </c>
       <c r="C36">
-        <v>305.6935026325128</v>
+        <v>36.91327428958848</v>
       </c>
       <c r="D36">
-        <v>0.003191917872456207</v>
+        <v>0.0003723530379681206</v>
       </c>
       <c r="E36">
-        <v>0.9968080821275438</v>
+        <v>0.9996276469620319</v>
       </c>
       <c r="F36">
-        <v>39.83752774061823</v>
+        <v>52.15162756260975</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1117,19 +1117,19 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>95465.4117850105</v>
+        <v>99098.23677314699</v>
       </c>
       <c r="C37">
-        <v>325.3455574876707</v>
+        <v>38.77180824259952</v>
       </c>
       <c r="D37">
-        <v>0.003407994072453735</v>
+        <v>0.0003912461967547909</v>
       </c>
       <c r="E37">
-        <v>0.9965920059275463</v>
+        <v>0.9996087538032452</v>
       </c>
       <c r="F37">
-        <v>38.96349196593381</v>
+        <v>51.17086736704832</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1137,19 +1137,19 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>95140.06622752282</v>
+        <v>99059.46496490439</v>
       </c>
       <c r="C38">
-        <v>346.2283760065334</v>
+        <v>40.86021462610606</v>
       </c>
       <c r="D38">
-        <v>0.003639143735495676</v>
+        <v>0.000412481680984067</v>
       </c>
       <c r="E38">
-        <v>0.9963608562645043</v>
+        <v>0.9995875183190159</v>
       </c>
       <c r="F38">
-        <v>38.09502357751219</v>
+        <v>50.19069991059919</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1157,19 +1157,19 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>94793.83785151629</v>
+        <v>99018.60475027827</v>
       </c>
       <c r="C39">
-        <v>368.4081460968807</v>
+        <v>43.20675102869054</v>
       </c>
       <c r="D39">
-        <v>0.003886414501688917</v>
+        <v>0.0004363498267588861</v>
       </c>
       <c r="E39">
-        <v>0.9961135854983111</v>
+        <v>0.9995636501732411</v>
       </c>
       <c r="F39">
-        <v>37.23233697524125</v>
+        <v>49.2112048719485</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1177,19 +1177,19 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>94425.42970541942</v>
+        <v>98975.39799924959</v>
       </c>
       <c r="C40">
-        <v>391.952995961472</v>
+        <v>45.84312220818751</v>
       </c>
       <c r="D40">
-        <v>0.004150926261964116</v>
+        <v>0.0004631769422996923</v>
       </c>
       <c r="E40">
-        <v>0.9958490737380359</v>
+        <v>0.9995368230577003</v>
       </c>
       <c r="F40">
-        <v>36.37565104020311</v>
+        <v>48.23246927647482</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1197,19 +1197,19 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>94033.47670945794</v>
+        <v>98929.5548770414</v>
       </c>
       <c r="C41">
-        <v>416.9327811511048</v>
+        <v>48.80489363396037</v>
       </c>
       <c r="D41">
-        <v>0.0044338760592606</v>
+        <v>0.0004933297607031539</v>
       </c>
       <c r="E41">
-        <v>0.9955661239407394</v>
+        <v>0.9995066702392968</v>
       </c>
       <c r="F41">
-        <v>35.52518894307917</v>
+        <v>47.25458810057203</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1217,19 +1217,19 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>93616.54392830684</v>
+        <v>98880.74998340744</v>
       </c>
       <c r="C42">
-        <v>443.4188148763046</v>
+        <v>52.13195279015003</v>
       </c>
       <c r="D42">
-        <v>0.004736543310292274</v>
+        <v>0.0005272204427949623</v>
       </c>
       <c r="E42">
-        <v>0.9952634566897077</v>
+        <v>0.999472779557205</v>
       </c>
       <c r="F42">
-        <v>34.68117792562016</v>
+        <v>46.27766491481071</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1237,19 +1237,19 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>93173.12511343053</v>
+        <v>98828.61803061729</v>
       </c>
       <c r="C43">
-        <v>471.4835333505548</v>
+        <v>55.86902325921151</v>
       </c>
       <c r="D43">
-        <v>0.005060295367108947</v>
+        <v>0.0005653121977472475</v>
       </c>
       <c r="E43">
-        <v>0.9949397046328911</v>
+        <v>0.9994346878022528</v>
       </c>
       <c r="F43">
-        <v>33.84384905410708</v>
+        <v>45.30181256671293</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1257,19 +1257,19 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>92701.64158007997</v>
+        <v>98772.74900735808</v>
       </c>
       <c r="C44">
-        <v>501.2000871101878</v>
+        <v>60.06623699527086</v>
       </c>
       <c r="D44">
-        <v>0.00540659343855554</v>
+        <v>0.0006081255973831023</v>
       </c>
       <c r="E44">
-        <v>0.9945934065614445</v>
+        <v>0.9993918744026169</v>
       </c>
       <c r="F44">
-        <v>33.01343694380974</v>
+        <v>44.32715390360494</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1277,19 +1277,19 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>92200.44149296978</v>
+        <v>98712.68277036281</v>
       </c>
       <c r="C45">
-        <v>532.6418484030771</v>
+        <v>64.7797705755454</v>
       </c>
       <c r="D45">
-        <v>0.005776998892610408</v>
+        <v>0.0006562456693254282</v>
       </c>
       <c r="E45">
-        <v>0.9942230011073896</v>
+        <v>0.9993437543306746</v>
       </c>
       <c r="F45">
-        <v>32.1901794535485</v>
+        <v>43.35382253563195</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1297,19 +1297,19 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>91667.79964456671</v>
+        <v>98647.90299978726</v>
       </c>
       <c r="C46">
-        <v>565.8818238768519</v>
+        <v>70.07255156888313</v>
       </c>
       <c r="D46">
-        <v>0.006173179961458719</v>
+        <v>0.0007103298644780542</v>
       </c>
       <c r="E46">
-        <v>0.9938268200385413</v>
+        <v>0.9992896701355219</v>
       </c>
       <c r="F46">
-        <v>31.37431734957974</v>
+        <v>42.38196363856191</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1317,19 +1317,19 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>91101.91782068985</v>
+        <v>98577.83044821837</v>
       </c>
       <c r="C47">
-        <v>600.9919609467911</v>
+        <v>76.01504146213773</v>
       </c>
       <c r="D47">
-        <v>0.006596918872000979</v>
+        <v>0.0007711170058877226</v>
       </c>
       <c r="E47">
-        <v>0.993403081127999</v>
+        <v>0.9992288829941123</v>
       </c>
       <c r="F47">
-        <v>30.56609393815958</v>
+        <v>41.41173479545921</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1337,19 +1337,19 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>90500.92585974306</v>
+        <v>98501.81540675624</v>
       </c>
       <c r="C48">
-        <v>638.0423354123928</v>
+        <v>82.68610180573953</v>
       </c>
       <c r="D48">
-        <v>0.007050119425310863</v>
+        <v>0.0008394373389393195</v>
       </c>
       <c r="E48">
-        <v>0.9929498805746891</v>
+        <v>0.9991605626610607</v>
       </c>
       <c r="F48">
-        <v>29.765754666293</v>
+        <v>40.44330687566832</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1357,19 +1357,19 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>89862.88352433067</v>
+        <v>98419.1293049505</v>
       </c>
       <c r="C49">
-        <v>677.1002071538452</v>
+        <v>90.17395034379679</v>
       </c>
       <c r="D49">
-        <v>0.007534815049313637</v>
+        <v>0.000916223817266193</v>
       </c>
       <c r="E49">
-        <v>0.9924651849506864</v>
+        <v>0.9990837761827338</v>
       </c>
       <c r="F49">
-        <v>28.97354669034742</v>
+        <v>39.47686494880007</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1377,19 +1377,19 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>89185.78331717683</v>
+        <v>98328.9553546067</v>
       </c>
       <c r="C50">
-        <v>718.2289301203692</v>
+        <v>98.57721382670125</v>
       </c>
       <c r="D50">
-        <v>0.008053177349646501</v>
+        <v>0.001002524774835645</v>
       </c>
       <c r="E50">
-        <v>0.9919468226503535</v>
+        <v>0.9989974752251644</v>
       </c>
       <c r="F50">
-        <v>28.18971841240176</v>
+        <v>38.51260923055081</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1397,19 +1397,19 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>88467.55438705646</v>
+        <v>98230.37814078</v>
       </c>
       <c r="C51">
-        <v>761.4867023762833</v>
+        <v>108.006083903227</v>
       </c>
       <c r="D51">
-        <v>0.00860752518425778</v>
+        <v>0.001099518152606893</v>
       </c>
       <c r="E51">
-        <v>0.9913924748157422</v>
+        <v>0.9989004818473931</v>
       </c>
       <c r="F51">
-        <v>27.41451898441331</v>
+        <v>37.55075605619838</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1417,19 +1417,19 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>87706.06768468018</v>
+        <v>98122.37205687677</v>
       </c>
       <c r="C52">
-        <v>806.9251417656774</v>
+        <v>118.5835818678643</v>
       </c>
       <c r="D52">
-        <v>0.009200334287779555</v>
+        <v>0.001208527468120391</v>
       </c>
       <c r="E52">
-        <v>0.9907996657122204</v>
+        <v>0.9987914725318796</v>
       </c>
       <c r="F52">
-        <v>26.64819778051632</v>
+        <v>36.59153887650121</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1437,19 +1437,19 @@
         <v>51</v>
       </c>
       <c r="B53">
-        <v>86899.1425429145</v>
+        <v>98003.78847500891</v>
       </c>
       <c r="C53">
-        <v>854.5876728754076</v>
+        <v>130.4469369913162</v>
       </c>
       <c r="D53">
-        <v>0.009834247472043534</v>
+        <v>0.001331039738576845</v>
       </c>
       <c r="E53">
-        <v>0.9901657525279565</v>
+        <v>0.9986689602614232</v>
       </c>
       <c r="F53">
-        <v>25.89100383801614</v>
+        <v>35.63520926946964</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1457,19 +1457,19 @@
         <v>52</v>
       </c>
       <c r="B54">
-        <v>86044.55487003909</v>
+        <v>97873.3415380176</v>
       </c>
       <c r="C54">
-        <v>904.5077115157237</v>
+        <v>143.7490815514412</v>
       </c>
       <c r="D54">
-        <v>0.01051208542925097</v>
+        <v>0.001468725592613018</v>
       </c>
       <c r="E54">
-        <v>0.989487914570749</v>
+        <v>0.998531274407387</v>
       </c>
       <c r="F54">
-        <v>25.14318526791225</v>
+        <v>34.68203796007863</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -1477,19 +1477,19 @@
         <v>53</v>
       </c>
       <c r="B55">
-        <v>85140.04715852338</v>
+        <v>97729.59245646615</v>
       </c>
       <c r="C55">
-        <v>956.706634017176</v>
+        <v>158.6602633374356</v>
       </c>
       <c r="D55">
-        <v>0.01123685816424169</v>
+        <v>0.001623461833304085</v>
       </c>
       <c r="E55">
-        <v>0.9887631418357583</v>
+        <v>0.9983765381666959</v>
       </c>
       <c r="F55">
-        <v>24.40498863606915</v>
+        <v>33.73231583844497</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1497,19 +1497,19 @@
         <v>54</v>
       </c>
       <c r="B56">
-        <v>84183.3405245062</v>
+        <v>97570.93219312871</v>
       </c>
       <c r="C56">
-        <v>1011.191520394986</v>
+        <v>175.3697731078956</v>
       </c>
       <c r="D56">
-        <v>0.01201177708195866</v>
+        <v>0.001797356745150025</v>
       </c>
       <c r="E56">
-        <v>0.9879882229180413</v>
+        <v>0.99820264325485</v>
       </c>
       <c r="F56">
-        <v>23.67665831645649</v>
+        <v>32.78635496530094</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1517,19 +1517,19 @@
         <v>55</v>
       </c>
       <c r="B57">
-        <v>83172.14900411121</v>
+        <v>97395.56242002081</v>
       </c>
       <c r="C57">
-        <v>1067.952663016599</v>
+        <v>194.0877799782701</v>
       </c>
       <c r="D57">
-        <v>0.0128402677555417</v>
+        <v>0.00199277847117163</v>
       </c>
       <c r="E57">
-        <v>0.9871597322444583</v>
+        <v>0.9980072215288284</v>
       </c>
       <c r="F57">
-        <v>22.9584358181961</v>
+        <v>31.84448955176525</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -1537,19 +1537,19 @@
         <v>56</v>
       </c>
       <c r="B58">
-        <v>82104.19634109462</v>
+        <v>97201.47464004254</v>
       </c>
       <c r="C58">
-        <v>1126.960836001979</v>
+        <v>215.0472616677226</v>
       </c>
       <c r="D58">
-        <v>0.01372598339943698</v>
+        <v>0.00221238682297864</v>
       </c>
       <c r="E58">
-        <v>0.986274016600563</v>
+        <v>0.9977876131770214</v>
       </c>
       <c r="F58">
-        <v>22.25055908848046</v>
+        <v>30.90707689845091</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -1557,19 +1557,19 @@
         <v>57</v>
       </c>
       <c r="B59">
-        <v>80977.23550509264</v>
+        <v>96986.42737837481</v>
       </c>
       <c r="C59">
-        <v>1188.164325387348</v>
+        <v>238.5060085499472</v>
       </c>
       <c r="D59">
-        <v>0.01467281907039941</v>
+        <v>0.002459168927003152</v>
       </c>
       <c r="E59">
-        <v>0.9853271809296006</v>
+        <v>0.9975408310729968</v>
       </c>
       <c r="F59">
-        <v>21.55326179376512</v>
+        <v>29.97449827687556</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -1577,19 +1577,19 @@
         <v>58</v>
       </c>
       <c r="B60">
-        <v>79789.07117970529</v>
+        <v>96747.92136982486</v>
       </c>
       <c r="C60">
-        <v>1251.485726310962</v>
+        <v>264.7486700409052</v>
       </c>
       <c r="D60">
-        <v>0.01568492661723431</v>
+        <v>0.002736479154202054</v>
       </c>
       <c r="E60">
-        <v>0.9843150733827657</v>
+        <v>0.9972635208457979</v>
       </c>
       <c r="F60">
-        <v>20.86677258197887</v>
+        <v>29.04715973397454</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1597,19 +1597,19 @@
         <v>59</v>
       </c>
       <c r="B61">
-        <v>78537.58545339433</v>
+        <v>96483.17269978396</v>
       </c>
       <c r="C61">
-        <v>1316.81852136393</v>
+        <v>294.0887984360795</v>
       </c>
       <c r="D61">
-        <v>0.01676673039745225</v>
+        <v>0.003048083828577686</v>
       </c>
       <c r="E61">
-        <v>0.9832332696025478</v>
+        <v>0.9969519161714223</v>
       </c>
       <c r="F61">
-        <v>20.19131432884086</v>
+        <v>28.12549279829583</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -1617,19 +1617,19 @@
         <v>60</v>
       </c>
       <c r="B62">
-        <v>77220.7669320304</v>
+        <v>96189.08390134788</v>
       </c>
       <c r="C62">
-        <v>1384.023464032941</v>
+        <v>326.8708281901125</v>
       </c>
       <c r="D62">
-        <v>0.01792294377561876</v>
+        <v>0.003398211261948947</v>
       </c>
       <c r="E62">
-        <v>0.9820770562243812</v>
+        <v>0.9966017887380511</v>
       </c>
       <c r="F62">
-        <v>19.52710337171634</v>
+        <v>27.2099550642177</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -1637,19 +1637,19 @@
         <v>61</v>
       </c>
       <c r="B63">
-        <v>75836.74346799745</v>
+        <v>95862.21307315778</v>
       </c>
       <c r="C63">
-        <v>1452.924803082551</v>
+        <v>363.4719070015345</v>
       </c>
       <c r="D63">
-        <v>0.01915858641392842</v>
+        <v>0.003791607718508949</v>
       </c>
       <c r="E63">
-        <v>0.9808414135860716</v>
+        <v>0.9962083922814911</v>
       </c>
       <c r="F63">
-        <v>18.87434873477902</v>
+        <v>26.30103062833073</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -1657,19 +1657,19 @@
         <v>62</v>
       </c>
       <c r="B64">
-        <v>74383.8186649149</v>
+        <v>95498.74116615624</v>
       </c>
       <c r="C64">
-        <v>1523.306398007207</v>
+        <v>404.3034679956312</v>
       </c>
       <c r="D64">
-        <v>0.02047900236030387</v>
+        <v>0.004233599972717883</v>
       </c>
       <c r="E64">
-        <v>0.9795209976396961</v>
+        <v>0.9957664000272821</v>
       </c>
       <c r="F64">
-        <v>18.23325134957367</v>
+        <v>25.39923035002934</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -1677,19 +1677,19 @@
         <v>63</v>
       </c>
       <c r="B65">
-        <v>72860.5122669077</v>
+        <v>95094.4376981606</v>
       </c>
       <c r="C65">
-        <v>1594.907792515265</v>
+        <v>449.8123987439124</v>
       </c>
       <c r="D65">
-        <v>0.02188987893294914</v>
+        <v>0.004730165187701751</v>
       </c>
       <c r="E65">
-        <v>0.9781101210670509</v>
+        <v>0.9952698348122982</v>
       </c>
       <c r="F65">
-        <v>17.60400327538114</v>
+        <v>24.50509190644226</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -1697,19 +1697,19 @@
         <v>64</v>
       </c>
       <c r="B66">
-        <v>71265.60447439243</v>
+        <v>94644.62529941669</v>
       </c>
       <c r="C66">
-        <v>1667.420332517737</v>
+        <v>500.4816216792419</v>
       </c>
       <c r="D66">
-        <v>0.02339726639260997</v>
+        <v>0.00528800890801695</v>
       </c>
       <c r="E66">
-        <v>0.97660273360739</v>
+        <v>0.994711991091983</v>
       </c>
       <c r="F66">
-        <v>16.98678692407543</v>
+        <v>23.61917961019031</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -1717,19 +1717,19 @@
         <v>65</v>
       </c>
       <c r="B67">
-        <v>69598.18414187469</v>
+        <v>94144.14367773745</v>
       </c>
       <c r="C67">
-        <v>1740.48343731896</v>
+        <v>556.8298504742046</v>
       </c>
       <c r="D67">
-        <v>0.02500759838462185</v>
+        <v>0.005914652029554546</v>
       </c>
       <c r="E67">
-        <v>0.9749924016153781</v>
+        <v>0.9940853479704455</v>
       </c>
       <c r="F67">
-        <v>16.38177429442193</v>
+        <v>22.74208395719685</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -1737,19 +1737,19 @@
         <v>66</v>
       </c>
       <c r="B68">
-        <v>67857.70070455573</v>
+        <v>93587.31382726325</v>
       </c>
       <c r="C68">
-        <v>1813.68115754562</v>
+        <v>619.4102269918658</v>
       </c>
       <c r="D68">
-        <v>0.02672771312193689</v>
+        <v>0.006618527679244313</v>
       </c>
       <c r="E68">
-        <v>0.9732722868780631</v>
+        <v>0.9933814723207557</v>
       </c>
       <c r="F68">
-        <v>15.78912622099292</v>
+        <v>21.87442087101169</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -1757,19 +1757,19 @@
         <v>67</v>
       </c>
       <c r="B69">
-        <v>66044.0195470101</v>
+        <v>92967.90360027138</v>
       </c>
       <c r="C69">
-        <v>1886.539180523756</v>
+        <v>688.8074725005456</v>
       </c>
       <c r="D69">
-        <v>0.02856487526748608</v>
+        <v>0.00740908900626791</v>
       </c>
       <c r="E69">
-        <v>0.9714351247325139</v>
+        <v>0.9925909109937321</v>
       </c>
       <c r="F69">
-        <v>15.20899164306364</v>
+        <v>21.01683060997341</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -1777,19 +1777,19 @@
         <v>68</v>
       </c>
       <c r="B70">
-        <v>64157.48036648634</v>
+        <v>92279.09612777084</v>
       </c>
       <c r="C70">
-        <v>1958.522472796522</v>
+        <v>765.6331043484141</v>
       </c>
       <c r="D70">
-        <v>0.03052679845917994</v>
+        <v>0.008296928952233218</v>
       </c>
       <c r="E70">
-        <v>0.9694732015408201</v>
+        <v>0.9917030710477668</v>
       </c>
       <c r="F70">
-        <v>14.64150689899521</v>
+        <v>20.16997630416844</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -1797,19 +1797,19 @@
         <v>69</v>
       </c>
       <c r="B71">
-        <v>62198.95789368982</v>
+        <v>91513.46302342243</v>
       </c>
       <c r="C71">
-        <v>2029.033779438385</v>
+        <v>850.5181752728965</v>
       </c>
       <c r="D71">
-        <v>0.03262166840329384</v>
+        <v>0.009293913126806386</v>
       </c>
       <c r="E71">
-        <v>0.9673783315967062</v>
+        <v>0.9907060868731936</v>
       </c>
       <c r="F71">
-        <v>14.08679505170394</v>
+        <v>19.33454209069502</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -1817,19 +1817,19 @@
         <v>70</v>
       </c>
       <c r="B72">
-        <v>60169.92411425144</v>
+        <v>90662.94484814953</v>
       </c>
       <c r="C72">
-        <v>2097.413229552878</v>
+        <v>944.1028881455758</v>
       </c>
       <c r="D72">
-        <v>0.03485816644159767</v>
+        <v>0.01041332696314734</v>
       </c>
       <c r="E72">
-        <v>0.9651418335584023</v>
+        <v>0.9895866730368527</v>
       </c>
       <c r="F72">
-        <v>13.54496525085306</v>
+        <v>18.51123081835447</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -1837,19 +1837,19 @@
         <v>71</v>
       </c>
       <c r="B73">
-        <v>58072.51088469856</v>
+        <v>89718.84196000396</v>
       </c>
       <c r="C73">
-        <v>2162.939325176322</v>
+        <v>1047.022327126771</v>
       </c>
       <c r="D73">
-        <v>0.03724549347402561</v>
+        <v>0.01167003835820268</v>
       </c>
       <c r="E73">
-        <v>0.9627545065259744</v>
+        <v>0.9883299616417973</v>
       </c>
       <c r="F73">
-        <v>13.01611213738119</v>
+        <v>17.70076129671536</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -1857,19 +1857,19 @@
         <v>72</v>
       </c>
       <c r="B74">
-        <v>55909.57155952224</v>
+        <v>88671.81963287719</v>
       </c>
       <c r="C74">
-        <v>2224.831614558189</v>
+        <v>1159.887432394665</v>
       </c>
       <c r="D74">
-        <v>0.03979339409155724</v>
+        <v>0.01308067700873716</v>
       </c>
       <c r="E74">
-        <v>0.9602066059084428</v>
+        <v>0.9869193229912628</v>
       </c>
       <c r="F74">
-        <v>12.50031529589471</v>
+        <v>16.90386506965927</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -1877,19 +1877,19 @@
         <v>73</v>
       </c>
       <c r="B75">
-        <v>53684.73994496404</v>
+        <v>87511.93220048252</v>
       </c>
       <c r="C75">
-        <v>2282.255367674975</v>
+        <v>1283.260238960788</v>
       </c>
       <c r="D75">
-        <v>0.04251218074288288</v>
+        <v>0.01466383162493712</v>
       </c>
       <c r="E75">
-        <v>0.9574878192571171</v>
+        <v>0.9853361683750629</v>
       </c>
       <c r="F75">
-        <v>11.99763876029714</v>
+        <v>16.12128270013059</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -1897,19 +1897,19 @@
         <v>74</v>
       </c>
       <c r="B76">
-        <v>51402.48457728907</v>
+        <v>86228.67196152173</v>
       </c>
       <c r="C76">
-        <v>2334.328578464405</v>
+        <v>1417.622314800884</v>
       </c>
       <c r="D76">
-        <v>0.04541275772291697</v>
+        <v>0.01644026612671801</v>
       </c>
       <c r="E76">
-        <v>0.954587242277083</v>
+        <v>0.983559733873282</v>
       </c>
       <c r="F76">
-        <v>11.50813057780491</v>
+        <v>15.35375956095467</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -1917,19 +1917,19 @@
         <v>75</v>
       </c>
       <c r="B77">
-        <v>49068.15599882467</v>
+        <v>84811.04964672084</v>
       </c>
       <c r="C77">
-        <v>2380.131610631949</v>
+        <v>1563.335290620649</v>
       </c>
       <c r="D77">
-        <v>0.04850664473083033</v>
+        <v>0.01843315578727889</v>
       </c>
       <c r="E77">
-        <v>0.9514933552691697</v>
+        <v>0.9815668442127211</v>
       </c>
       <c r="F77">
-        <v>11.03182243620395</v>
+        <v>14.60204113629195</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -1937,19 +1937,19 @@
         <v>76</v>
       </c>
       <c r="B78">
-        <v>46688.02438819272</v>
+        <v>83247.71435610019</v>
       </c>
       <c r="C78">
-        <v>2418.719777425104</v>
+        <v>1720.59240281539</v>
       </c>
       <c r="D78">
-        <v>0.05180599969950306</v>
+        <v>0.02066834406354257</v>
       </c>
       <c r="E78">
-        <v>0.9481940003004969</v>
+        <v>0.9793316559364574</v>
       </c>
       <c r="F78">
-        <v>10.56872935883465</v>
+        <v>13.86686784953773</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -1957,19 +1957,19 @@
         <v>77</v>
       </c>
       <c r="B79">
-        <v>44269.30461076761</v>
+        <v>81527.12195328479</v>
       </c>
       <c r="C79">
-        <v>2449.13909553661</v>
+        <v>1889.360113222323</v>
       </c>
       <c r="D79">
-        <v>0.05532364054665784</v>
+        <v>0.02317462051837094</v>
       </c>
       <c r="E79">
-        <v>0.9446763594533422</v>
+        <v>0.9768253794816291</v>
       </c>
       <c r="F79">
-        <v>10.11884947135683</v>
+        <v>13.14896944616382</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -1977,19 +1977,19 @@
         <v>78</v>
       </c>
       <c r="B80">
-        <v>41820.165515231</v>
+        <v>79637.76184006246</v>
       </c>
       <c r="C80">
-        <v>2470.445374187933</v>
+        <v>2069.309177549417</v>
       </c>
       <c r="D80">
-        <v>0.05907306543988189</v>
+        <v>0.02598401976320275</v>
       </c>
       <c r="E80">
-        <v>0.9409269345601181</v>
+        <v>0.9740159802367973</v>
       </c>
       <c r="F80">
-        <v>9.68216384384065</v>
+        <v>12.44905897395524</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -1997,19 +1997,19 @@
         <v>79</v>
       </c>
       <c r="B81">
-        <v>39349.72014104307</v>
+        <v>77568.45266251305</v>
       </c>
       <c r="C81">
-        <v>2481.726687618262</v>
+        <v>2259.735076312524</v>
       </c>
       <c r="D81">
-        <v>0.06306847110279035</v>
+        <v>0.02913214069312742</v>
       </c>
       <c r="E81">
-        <v>0.9369315288972097</v>
+        <v>0.9708678593068726</v>
       </c>
       <c r="F81">
-        <v>9.258636411161191</v>
+        <v>11.76782641805348</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2017,19 +2017,19 @@
         <v>80</v>
       </c>
       <c r="B82">
-        <v>36867.99345342481</v>
+        <v>75308.71758620052</v>
       </c>
       <c r="C82">
-        <v>2482.129128633119</v>
+        <v>2459.468578625294</v>
       </c>
       <c r="D82">
-        <v>0.06732476861722303</v>
+        <v>0.03265848440202312</v>
       </c>
       <c r="E82">
-        <v>0.932675231382777</v>
+        <v>0.9673415155979769</v>
       </c>
       <c r="F82">
-        <v>8.848213974046013</v>
+        <v>11.10593206381131</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2037,19 +2037,19 @@
         <v>81</v>
       </c>
       <c r="B83">
-        <v>34385.86432479169</v>
+        <v>72849.24900757523</v>
       </c>
       <c r="C83">
-        <v>2470.885550067378</v>
+        <v>2666.778471084772</v>
       </c>
       <c r="D83">
-        <v>0.07185759609613496</v>
+        <v>0.03660680799616023</v>
       </c>
       <c r="E83">
-        <v>0.928142403903865</v>
+        <v>0.9633931920038398</v>
       </c>
       <c r="F83">
-        <v>8.450826282444552</v>
+        <v>10.46399967622096</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2057,19 +2057,19 @@
         <v>82</v>
       </c>
       <c r="B84">
-        <v>31914.97877472431</v>
+        <v>70182.47053649045</v>
       </c>
       <c r="C84">
-        <v>2447.346769964409</v>
+        <v>2879.270243354999</v>
       </c>
       <c r="D84">
-        <v>0.07668332751336915</v>
+        <v>0.04102549000263478</v>
       </c>
       <c r="E84">
-        <v>0.9233166724866309</v>
+        <v>0.9589745099973652</v>
       </c>
       <c r="F84">
-        <v>8.066386202163097</v>
+        <v>9.842609600028446</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2077,19 +2077,19 @@
         <v>83</v>
       </c>
       <c r="B85">
-        <v>29467.6320047599</v>
+        <v>67303.20029313545</v>
       </c>
       <c r="C85">
-        <v>2411.014448453616</v>
+        <v>3093.786855754113</v>
       </c>
       <c r="D85">
-        <v>0.08181907687947798</v>
+        <v>0.04596790111434956</v>
       </c>
       <c r="E85">
-        <v>0.918180923120522</v>
+        <v>0.9540320988856504</v>
       </c>
       <c r="F85">
-        <v>7.694789964948515</v>
+        <v>9.24229189893078</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2097,19 +2097,19 @@
         <v>84</v>
       </c>
       <c r="B86">
-        <v>27056.61755630629</v>
+        <v>64209.41343738134</v>
       </c>
       <c r="C86">
-        <v>2361.574547873419</v>
+        <v>3306.320656460233</v>
       </c>
       <c r="D86">
-        <v>0.08728269684704137</v>
+        <v>0.05149277153395337</v>
       </c>
       <c r="E86">
-        <v>0.9127173031529586</v>
+        <v>0.9485072284660466</v>
       </c>
       <c r="F86">
-        <v>7.335917501418305</v>
+        <v>8.663519664738896</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2117,19 +2117,19 @@
         <v>85</v>
       </c>
       <c r="B87">
-        <v>24695.04300843287</v>
+        <v>60903.09278092111</v>
       </c>
       <c r="C87">
-        <v>2298.929976570143</v>
+        <v>3511.949016842887</v>
       </c>
       <c r="D87">
-        <v>0.09309277071455613</v>
+        <v>0.05766454307133417</v>
       </c>
       <c r="E87">
-        <v>0.9069072292854439</v>
+        <v>0.9423354569286658</v>
       </c>
       <c r="F87">
-        <v>6.989632855434868</v>
+        <v>8.10670263730217</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2137,19 +2137,19 @@
         <v>86</v>
       </c>
       <c r="B88">
-        <v>22396.11303186272</v>
+        <v>57391.14376407822</v>
       </c>
       <c r="C88">
-        <v>2223.230711652836</v>
+        <v>3704.810120460977</v>
       </c>
       <c r="D88">
-        <v>0.09926859667522969</v>
+        <v>0.0645536902991618</v>
       </c>
       <c r="E88">
-        <v>0.9007314033247703</v>
+        <v>0.9354463097008382</v>
       </c>
       <c r="F88">
-        <v>6.655784677720651</v>
+        <v>7.572181282549356</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2157,19 +2157,19 @@
         <v>87</v>
       </c>
       <c r="B89">
-        <v>20172.88232020989</v>
+        <v>53686.33364361724</v>
       </c>
       <c r="C89">
-        <v>2134.899424662352</v>
+        <v>3878.139165823952</v>
       </c>
       <c r="D89">
-        <v>0.1058301630265069</v>
+        <v>0.07223699035899844</v>
       </c>
       <c r="E89">
-        <v>0.8941698369734931</v>
+        <v>0.9277630096410016</v>
       </c>
       <c r="F89">
-        <v>6.3342067957201</v>
+        <v>7.060221478463134</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -2177,19 +2177,19 @@
         <v>88</v>
       </c>
       <c r="B90">
-        <v>18037.98289554754</v>
+        <v>49808.19447779329</v>
       </c>
       <c r="C90">
-        <v>2034.650431481878</v>
+        <v>4024.388317951662</v>
       </c>
       <c r="D90">
-        <v>0.1127981129189399</v>
+        <v>0.08079771531862923</v>
       </c>
       <c r="E90">
-        <v>0.8872018870810601</v>
+        <v>0.9192022846813708</v>
       </c>
       <c r="F90">
-        <v>6.024718855947106</v>
+        <v>6.571009956520703</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2197,19 +2197,19 @@
         <v>89</v>
       </c>
       <c r="B91">
-        <v>16003.33246406566</v>
+        <v>45783.80615984162</v>
       </c>
       <c r="C91">
-        <v>1923.49969446613</v>
+        <v>4135.454990417877</v>
       </c>
       <c r="D91">
-        <v>0.1201936970806057</v>
+        <v>0.09032571420515079</v>
       </c>
       <c r="E91">
-        <v>0.8798063029193943</v>
+        <v>0.9096742857948492</v>
       </c>
       <c r="F91">
-        <v>5.727127034325541</v>
+        <v>6.104650638597072</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2217,19 +2217,19 @@
         <v>90</v>
       </c>
       <c r="B92">
-        <v>14079.83276959953</v>
+        <v>41648.35116942375</v>
       </c>
       <c r="C92">
-        <v>1802.763664369774</v>
+        <v>4203.040978083322</v>
       </c>
       <c r="D92">
-        <v>0.128038712807883</v>
+        <v>0.1009173439060175</v>
       </c>
       <c r="E92">
-        <v>0.871961287192117</v>
+        <v>0.8990826560939825</v>
       </c>
       <c r="F92">
-        <v>5.441224809348106</v>
+        <v>5.66116199624119</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2237,19 +2237,19 @@
         <v>91</v>
       </c>
       <c r="B93">
-        <v>12277.06910522975</v>
+        <v>37445.31019134042</v>
       </c>
       <c r="C93">
-        <v>1674.045004669849</v>
+        <v>4219.157778535268</v>
       </c>
       <c r="D93">
-        <v>0.1363554273679818</v>
+        <v>0.1126751990296234</v>
       </c>
       <c r="E93">
-        <v>0.8636445726320182</v>
+        <v>0.8873248009703766</v>
       </c>
       <c r="F93">
-        <v>5.166793792256307</v>
+        <v>5.240475540551064</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2257,19 +2257,19 @@
         <v>92</v>
       </c>
       <c r="B94">
-        <v>10603.02410055991</v>
+        <v>33226.15241280515</v>
       </c>
       <c r="C94">
-        <v>1539.203726505986</v>
+        <v>4176.779233632662</v>
       </c>
       <c r="D94">
-        <v>0.145166483817075</v>
+        <v>0.1257075806352757</v>
       </c>
       <c r="E94">
-        <v>0.854833516182925</v>
+        <v>0.8742924193647243</v>
       </c>
       <c r="F94">
-        <v>4.903604607893176</v>
+        <v>4.842435526840782</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -2277,19 +2277,19 @@
         <v>93</v>
       </c>
       <c r="B95">
-        <v>9063.820374053919</v>
+        <v>29049.37317917249</v>
       </c>
       <c r="C95">
-        <v>1400.312999049603</v>
+        <v>4070.619895601847</v>
       </c>
       <c r="D95">
-        <v>0.1544947871052407</v>
+        <v>0.1401276327201565</v>
       </c>
       <c r="E95">
-        <v>0.8455052128947593</v>
+        <v>0.8598723672798435</v>
       </c>
       <c r="F95">
-        <v>4.651417819409474</v>
+        <v>4.466799929474476</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -2297,19 +2297,19 @@
         <v>94</v>
       </c>
       <c r="B96">
-        <v>7663.507375004317</v>
+        <v>24978.75328357064</v>
       </c>
       <c r="C96">
-        <v>1259.599884549784</v>
+        <v>3897.986004901254</v>
       </c>
       <c r="D96">
-        <v>0.1643633682219917</v>
+        <v>0.1560520639540921</v>
       </c>
       <c r="E96">
-        <v>0.8356366317780083</v>
+        <v>0.8439479360459079</v>
       </c>
       <c r="F96">
-        <v>4.409984889621496</v>
+        <v>4.113242709523528</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2317,19 +2317,19 @@
         <v>95</v>
       </c>
       <c r="B97">
-        <v>6403.907490454533</v>
+        <v>21080.76727866939</v>
       </c>
       <c r="C97">
-        <v>1119.372444536985</v>
+        <v>3659.607732467544</v>
       </c>
       <c r="D97">
-        <v>0.1747952240418037</v>
+        <v>0.1735993611660674</v>
       </c>
       <c r="E97">
-        <v>0.8252047759581963</v>
+        <v>0.8264006388339326</v>
       </c>
       <c r="F97">
-        <v>4.179049171530583</v>
+        <v>3.781357362460543</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2337,19 +2337,19 @@
         <v>96</v>
       </c>
       <c r="B98">
-        <v>5284.535045917548</v>
+        <v>17421.15954620184</v>
       </c>
       <c r="C98">
-        <v>981.9359999460876</v>
+        <v>3360.322025718969</v>
       </c>
       <c r="D98">
-        <v>0.1858131304672983</v>
+        <v>0.1928873917265505</v>
       </c>
       <c r="E98">
-        <v>0.8141868695327017</v>
+        <v>0.8071126082734495</v>
       </c>
       <c r="F98">
-        <v>3.958346920324851</v>
+        <v>3.470661696354207</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -2357,19 +2357,19 @@
         <v>97</v>
       </c>
       <c r="B99">
-        <v>4302.59904597146</v>
+        <v>14060.83752048288</v>
       </c>
       <c r="C99">
-        <v>849.5026878814019</v>
+        <v>3009.445076195057</v>
       </c>
       <c r="D99">
-        <v>0.1974394264501115</v>
+        <v>0.2140302860203812</v>
       </c>
       <c r="E99">
-        <v>0.8025605735498885</v>
+        <v>0.7859697139796188</v>
       </c>
       <c r="F99">
-        <v>3.747608319094793</v>
+        <v>3.180603754547901</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -2377,19 +2377,19 @@
         <v>98</v>
       </c>
       <c r="B100">
-        <v>3453.096358090058</v>
+        <v>11051.39244428782</v>
       </c>
       <c r="C100">
-        <v>724.0996876412266</v>
+        <v>2620.666323890309</v>
       </c>
       <c r="D100">
-        <v>0.2096957665096069</v>
+        <v>0.2371344911604206</v>
       </c>
       <c r="E100">
-        <v>0.7903042334903931</v>
+        <v>0.7628655088395794</v>
       </c>
       <c r="F100">
-        <v>3.546558510505894</v>
+        <v>2.910568762217487</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -2397,19 +2397,19 @@
         <v>99</v>
       </c>
       <c r="B101">
-        <v>2728.996670448832</v>
+        <v>8430.726120397509</v>
       </c>
       <c r="C101">
-        <v>607.4824077827107</v>
+        <v>2211.328002702248</v>
       </c>
       <c r="D101">
-        <v>0.2226028394834206</v>
+        <v>0.2622938962934765</v>
       </c>
       <c r="E101">
-        <v>0.7773971605165794</v>
+        <v>0.7377061037065235</v>
       </c>
       <c r="F101">
-        <v>3.354918626780868</v>
+        <v>2.659886945058356</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -2417,19 +2417,19 @@
         <v>100</v>
       </c>
       <c r="B102">
-        <v>2121.514262666121</v>
+        <v>6219.39811769526</v>
       </c>
       <c r="C102">
-        <v>501.0593477077775</v>
+        <v>1801.03788958882</v>
       </c>
       <c r="D102">
-        <v>0.2361800514497098</v>
+        <v>0.2895839525796807</v>
       </c>
       <c r="E102">
-        <v>0.7638199485502902</v>
+        <v>0.7104160474203193</v>
       </c>
       <c r="F102">
-        <v>3.172406810546849</v>
+        <v>2.427842041981545</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -2437,19 +2437,19 @@
         <v>101</v>
       </c>
       <c r="B103">
-        <v>1620.454914958343</v>
+        <v>4418.36022810644</v>
       </c>
       <c r="C103">
-        <v>405.835108403661</v>
+        <v>1409.698828615678</v>
       </c>
       <c r="D103">
-        <v>0.2504451710796864</v>
+        <v>0.3190547524052441</v>
       </c>
       <c r="E103">
-        <v>0.7495548289203136</v>
+        <v>0.6809452475947559</v>
       </c>
       <c r="F103">
-        <v>2.998739219391961</v>
+        <v>2.213680313081291</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -2457,19 +2457,19 @@
         <v>102</v>
       </c>
       <c r="B104">
-        <v>1214.619806554682</v>
+        <v>3008.661399490763</v>
       </c>
       <c r="C104">
-        <v>322.3770237636083</v>
+        <v>1055.207048640793</v>
       </c>
       <c r="D104">
-        <v>0.2654139361336809</v>
+        <v>0.350723098591086</v>
       </c>
       <c r="E104">
-        <v>0.7345860638663191</v>
+        <v>0.649276901408914</v>
       </c>
       <c r="F104">
-        <v>2.833631007342368</v>
+        <v>2.016619829765133</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -2477,19 +2477,19 @@
         <v>103</v>
       </c>
       <c r="B105">
-        <v>892.242782791074</v>
+        <v>1953.454350849969</v>
       </c>
       <c r="C105">
-        <v>250.8091075737486</v>
+        <v>751.2276164020647</v>
       </c>
       <c r="D105">
-        <v>0.2810996204297431</v>
+        <v>0.3845636915319763</v>
       </c>
       <c r="E105">
-        <v>0.7189003795702569</v>
+        <v>0.6154363084680237</v>
       </c>
       <c r="F105">
-        <v>2.676797276904296</v>
+        <v>1.835859825713971</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -2497,19 +2497,19 @@
         <v>104</v>
       </c>
       <c r="B106">
-        <v>641.4336752173253</v>
+        <v>1202.226734447905</v>
       </c>
       <c r="C106">
-        <v>190.8345756932468</v>
+        <v>505.5359762712267</v>
       </c>
       <c r="D106">
-        <v>0.2975125614173434</v>
+        <v>0.4204996959274763</v>
       </c>
       <c r="E106">
-        <v>0.7024874385826566</v>
+        <v>0.5795003040725237</v>
       </c>
       <c r="F106">
-        <v>2.527953995803338</v>
+        <v>1.670589884498793</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -2517,19 +2517,19 @@
         <v>105</v>
       </c>
       <c r="B107">
-        <v>450.5990995240786</v>
+        <v>696.6907581766779</v>
       </c>
       <c r="C107">
-        <v>141.7853547246312</v>
+        <v>319.358252001969</v>
       </c>
       <c r="D107">
-        <v>0.3146596495074768</v>
+        <v>0.4583931224202935</v>
       </c>
       <c r="E107">
-        <v>0.6853403504925232</v>
+        <v>0.5416068775797065</v>
       </c>
       <c r="F107">
-        <v>2.386818873081847</v>
+        <v>1.519998740763896</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -2537,19 +2537,19 @@
         <v>106</v>
       </c>
       <c r="B108">
-        <v>308.8137447994473</v>
+        <v>377.3325061747089</v>
       </c>
       <c r="C108">
-        <v>102.694090496799</v>
+        <v>187.9250482328983</v>
       </c>
       <c r="D108">
-        <v>0.3325437815712885</v>
+        <v>0.4980356718747339</v>
       </c>
       <c r="E108">
-        <v>0.6674562184287115</v>
+        <v>0.5019643281252661</v>
       </c>
       <c r="F108">
-        <v>2.253112189769471</v>
+        <v>1.383282474775787</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -2557,19 +2557,19 @@
         <v>107</v>
       </c>
       <c r="B109">
-        <v>206.1196543026483</v>
+        <v>189.4074579418106</v>
       </c>
       <c r="C109">
-        <v>72.38165440235987</v>
+        <v>102.117313465306</v>
       </c>
       <c r="D109">
-        <v>0.3511632825469467</v>
+        <v>0.5391409323315997</v>
       </c>
       <c r="E109">
-        <v>0.6488367174530533</v>
+        <v>0.4608590676684003</v>
       </c>
       <c r="F109">
-        <v>2.126557579906215</v>
+        <v>1.259651882185864</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -2577,19 +2577,19 @@
         <v>108</v>
       </c>
       <c r="B110">
-        <v>133.7379999002884</v>
+        <v>87.29014447650458</v>
       </c>
       <c r="C110">
-        <v>49.55144032404993</v>
+        <v>50.74517144410657</v>
       </c>
       <c r="D110">
-        <v>0.370511300909197</v>
+        <v>0.5813390703891592</v>
       </c>
       <c r="E110">
-        <v>0.629488699090803</v>
+        <v>0.4186609296108408</v>
       </c>
       <c r="F110">
-        <v>2.006882758255593</v>
+        <v>1.148338799167237</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -2597,19 +2597,19 @@
         <v>109</v>
       </c>
       <c r="B111">
-        <v>84.18655957623849</v>
+        <v>36.544973032398</v>
       </c>
       <c r="C111">
-        <v>32.88118115431447</v>
+        <v>22.8104725649766</v>
       </c>
       <c r="D111">
-        <v>0.3905751858708231</v>
+        <v>0.6241753837047455</v>
       </c>
       <c r="E111">
-        <v>0.6094248141291769</v>
+        <v>0.3758246162952545</v>
       </c>
       <c r="F111">
-        <v>1.893820191580956</v>
+        <v>1.048601155044226</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -2617,19 +2617,19 @@
         <v>110</v>
       </c>
       <c r="B112">
-        <v>51.30537842192403</v>
+        <v>13.73450046742141</v>
       </c>
       <c r="C112">
-        <v>21.10374178148575</v>
+        <v>9.162480626789653</v>
       </c>
       <c r="D112">
-        <v>0.4113358566022702</v>
+        <v>0.6671142243959507</v>
       </c>
       <c r="E112">
-        <v>0.5886641433977298</v>
+        <v>0.3328857756040493</v>
       </c>
       <c r="F112">
-        <v>1.787107710854574</v>
+        <v>0.9597265087426701</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -2637,19 +2637,19 @@
         <v>111</v>
       </c>
       <c r="B113">
-        <v>30.20163664043827</v>
+        <v>4.572019840631752</v>
       </c>
       <c r="C113">
-        <v>13.07027701340797</v>
+        <v>3.244075717349274</v>
       </c>
       <c r="D113">
-        <v>0.4327671764618085</v>
+        <v>0.7095497899022709</v>
       </c>
       <c r="E113">
-        <v>0.5672328235381915</v>
+        <v>0.2904502100977291</v>
       </c>
       <c r="F113">
-        <v>1.686489062210372</v>
+        <v>0.8810338032872012</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -2657,19 +2657,19 @@
         <v>112</v>
       </c>
       <c r="B114">
-        <v>17.1313596270303</v>
+        <v>1.327944123282478</v>
       </c>
       <c r="C114">
-        <v>7.791947920935902</v>
+        <v>0.9970536724544408</v>
       </c>
       <c r="D114">
-        <v>0.4548353481904358</v>
+        <v>0.7508250196475692</v>
       </c>
       <c r="E114">
-        <v>0.5451646518095642</v>
+        <v>0.2491749803524308</v>
       </c>
       <c r="F114">
-        <v>1.591714394822016</v>
+        <v>0.8118730510093036</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -2677,19 +2677,19 @@
         <v>113</v>
       </c>
       <c r="B115">
-        <v>9.339411706094401</v>
+        <v>0.3308904508280375</v>
       </c>
       <c r="C115">
-        <v>4.459553672007787</v>
+        <v>0.2614892373852673</v>
       </c>
       <c r="D115">
-        <v>0.4774983491837843</v>
+        <v>0.7902592435983058</v>
       </c>
       <c r="E115">
-        <v>0.5225016508162157</v>
+        <v>0.2097407564016942</v>
       </c>
       <c r="F115">
-        <v>1.502540684173653</v>
+        <v>0.7516226571712508</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -2697,19 +2697,19 @@
         <v>114</v>
       </c>
       <c r="B116">
-        <v>4.879858034086614</v>
+        <v>0.06940121344277018</v>
       </c>
       <c r="C116">
-        <v>2.44337141147017</v>
+        <v>0.05740758992067914</v>
       </c>
       <c r="D116">
-        <v>0.5007054292159356</v>
+        <v>0.8271842389041042</v>
       </c>
       <c r="E116">
-        <v>0.4992945707840644</v>
+        <v>0.1728157610958958</v>
       </c>
       <c r="F116">
-        <v>1.418732089377237</v>
+        <v>0.6996841314395974</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -2717,19 +2717,19 @@
         <v>115</v>
       </c>
       <c r="B117">
-        <v>2.436486622616444</v>
+        <v>0.01199362352209104</v>
       </c>
       <c r="C117">
-        <v>1.277685535301723</v>
+        <v>0.01032635349284631</v>
       </c>
       <c r="D117">
-        <v>0.5243966962271553</v>
+        <v>0.8609869630997011</v>
       </c>
       <c r="E117">
-        <v>0.4756033037728447</v>
+        <v>0.1390130369002989</v>
       </c>
       <c r="F117">
-        <v>1.340060243263834</v>
+        <v>0.6554740735064797</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -2737,19 +2737,19 @@
         <v>116</v>
       </c>
       <c r="B118">
-        <v>1.158801087314721</v>
+        <v>0.001667270029244735</v>
       </c>
       <c r="C118">
-        <v>0.6356056628492537</v>
+        <v>0.001485796950216175</v>
       </c>
       <c r="D118">
-        <v>0.5485028188247016</v>
+        <v>0.8911555561814026</v>
       </c>
       <c r="E118">
-        <v>0.4514971811752984</v>
+        <v>0.1088444438185974</v>
       </c>
       <c r="F118">
-        <v>1.26630447391732</v>
+        <v>0.6184136176953448</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -2757,19 +2757,19 @@
         <v>117</v>
       </c>
       <c r="B119">
-        <v>0.5231954244654673</v>
+        <v>0.0001814730790285597</v>
       </c>
       <c r="C119">
-        <v>0.2997621379916046</v>
+        <v>0.0001664695198096652</v>
       </c>
       <c r="D119">
-        <v>0.5729448767596972</v>
+        <v>0.9173234988946578</v>
       </c>
       <c r="E119">
-        <v>0.4270551232403028</v>
+        <v>0.08267650110534219</v>
       </c>
       <c r="F119">
-        <v>1.197251956086509</v>
+        <v>0.5879160528643574</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -2777,19 +2777,19 @@
         <v>118</v>
       </c>
       <c r="B120">
-        <v>0.2234332864738627</v>
+        <v>1.500355921889457E-05</v>
       </c>
       <c r="C120">
-        <v>0.1335314164392539</v>
+        <v>1.409292574131231E-05</v>
       </c>
       <c r="D120">
-        <v>0.5976343925589369</v>
+        <v>0.9393055031611787</v>
       </c>
       <c r="E120">
-        <v>0.4023656074410631</v>
+        <v>0.06069449683882133</v>
       </c>
       <c r="F120">
-        <v>1.132697790383766</v>
+        <v>0.563374135201238</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -2797,19 +2797,19 @@
         <v>119</v>
       </c>
       <c r="B121">
-        <v>0.08990187003460882</v>
+        <v>9.106334775822652E-07</v>
       </c>
       <c r="C121">
-        <v>0.05596153874382179</v>
+        <v>8.715839944054233E-07</v>
       </c>
       <c r="D121">
-        <v>0.6224735783836166</v>
+        <v>0.9571183312077233</v>
       </c>
       <c r="E121">
-        <v>0.3775264216163834</v>
+        <v>0.04288166879227673</v>
       </c>
       <c r="F121">
-        <v>1.072445006936736</v>
+        <v>0.5441496099643551</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -2817,19 +2817,19 @@
         <v>120</v>
       </c>
       <c r="B122">
-        <v>0.03394033129078704</v>
+        <v>3.904948317684185E-08</v>
       </c>
       <c r="C122">
-        <v>0.02197147139053067</v>
+        <v>3.791629899364383E-08</v>
       </c>
       <c r="D122">
-        <v>0.6473558316885001</v>
+        <v>0.9709808148275302</v>
       </c>
       <c r="E122">
-        <v>0.3526441683114999</v>
+        <v>0.02901918517246982</v>
       </c>
       <c r="F122">
-        <v>1.016304486678857</v>
+        <v>0.5295683728686125</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -2837,19 +2837,19 @@
         <v>121</v>
       </c>
       <c r="B123">
-        <v>0.01196885990025637</v>
+        <v>1.133184183198019E-09</v>
       </c>
       <c r="C123">
-        <v>0.008045066799387993</v>
+        <v>1.111982490674401E-09</v>
       </c>
       <c r="D123">
-        <v>0.672166510965315</v>
+        <v>0.9812901619719194</v>
       </c>
       <c r="E123">
-        <v>0.327833489034685</v>
+        <v>0.01870983802808057</v>
       </c>
       <c r="F123">
-        <v>0.9640947818617868</v>
+        <v>0.5189249867933473</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -2857,19 +2857,19 @@
         <v>122</v>
       </c>
       <c r="B124">
-        <v>0.003923793100868378</v>
+        <v>2.120169252361771E-11</v>
       </c>
       <c r="C124">
-        <v>0.00273403632405266</v>
+        <v>2.095948418501194E-11</v>
       </c>
       <c r="D124">
-        <v>0.696784018364166</v>
+        <v>0.9885759904151068</v>
       </c>
       <c r="E124">
-        <v>0.303215981635834</v>
+        <v>0.0114240095848932</v>
       </c>
       <c r="F124">
-        <v>0.9156417735977097</v>
+        <v>0.5114992318449679</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -2877,19 +2877,19 @@
         <v>123</v>
       </c>
       <c r="B125">
-        <v>0.001189756776815718</v>
+        <v>2.422083386057672E-13</v>
       </c>
       <c r="C125">
-        <v>0.000857911254935346</v>
+        <v>2.406191003953305E-13</v>
       </c>
       <c r="D125">
-        <v>0.7210812089101706</v>
+        <v>0.9934385487321165</v>
       </c>
       <c r="E125">
-        <v>0.2789187910898294</v>
+        <v>0.006561451267883545</v>
       </c>
       <c r="F125">
-        <v>0.870777923232623</v>
+        <v>0.5065845760646212</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -2897,19 +2897,19 @@
         <v>124</v>
       </c>
       <c r="B126">
-        <v>0.0003318455218803721</v>
+        <v>1.589238210436778E-15</v>
       </c>
       <c r="C126">
-        <v>0.0002472007342250149</v>
+        <v>1.583646962613378E-15</v>
       </c>
       <c r="D126">
-        <v>0.7449271360489503</v>
+        <v>0.9964818063228775</v>
       </c>
       <c r="E126">
-        <v>0.2550728639510497</v>
+        <v>0.003518193677122472</v>
       </c>
       <c r="F126">
-        <v>0.8293400626894629</v>
+        <v>0.5035243417642672</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -2917,19 +2917,19 @@
         <v>125</v>
       </c>
       <c r="B127">
-        <v>8.464478765535722E-05</v>
+        <v>5.591247823400106E-18</v>
       </c>
       <c r="C127">
-        <v>6.502320580192157E-05</v>
+        <v>5.5814848078361E-18</v>
       </c>
       <c r="D127">
-        <v>0.7681891301644279</v>
+        <v>0.9982538753651472</v>
       </c>
       <c r="E127">
-        <v>0.2318108698355721</v>
+        <v>0.001746124634852797</v>
       </c>
       <c r="F127">
-        <v>0.7911607200704253</v>
+        <v>0.501747512419413</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -2937,19 +2937,19 @@
         <v>126</v>
       </c>
       <c r="B128">
-        <v>1.962158185343565E-05</v>
+        <v>9.763015564006006E-21</v>
       </c>
       <c r="C128">
-        <v>1.551547526482338E-05</v>
+        <v>9.755258660330479E-21</v>
       </c>
       <c r="D128">
-        <v>0.790735190501814</v>
+        <v>0.9992054807631234</v>
       </c>
       <c r="E128">
-        <v>0.209264809498186</v>
+        <v>0.0007945192368765674</v>
       </c>
       <c r="F128">
-        <v>0.7560270373729719</v>
+        <v>0.5007947797840027</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -2957,19 +2957,19 @@
         <v>127</v>
       </c>
       <c r="B129">
-        <v>4.106106588612276E-06</v>
+        <v>7.756903675528103E-24</v>
       </c>
       <c r="C129">
-        <v>3.33595148895662E-06</v>
+        <v>7.754360258289561E-24</v>
       </c>
       <c r="D129">
-        <v>0.8124366518415339</v>
+        <v>0.999672109214587</v>
       </c>
       <c r="E129">
-        <v>0.1875633481584661</v>
+        <v>0.0003278907854129542</v>
       </c>
       <c r="F129">
-        <v>0.7234595868599265</v>
+        <v>0.5003279305446376</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -2977,19 +2977,19 @@
         <v>128</v>
       </c>
       <c r="B130">
-        <v>7.701550996556558E-07</v>
+        <v>2.543417238541541E-27</v>
       </c>
       <c r="C130">
-        <v>6.416709452728503E-07</v>
+        <v>2.543108842288819E-27</v>
       </c>
       <c r="D130">
-        <v>0.8331710658797791</v>
+        <v>0.9998787472821807</v>
       </c>
       <c r="E130">
-        <v>0.1668289341202209</v>
+        <v>0.0001212527178192646</v>
       </c>
       <c r="F130">
-        <v>0.6913819467070551</v>
+        <v>0.5001212575236952</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -2997,19 +2997,19 @@
         <v>129</v>
       </c>
       <c r="B131">
-        <v>1.284841543828056E-07</v>
+        <v>3.083962527215307E-31</v>
       </c>
       <c r="C131">
-        <v>1.095745265271457E-07</v>
+        <v>3.083840293738347E-31</v>
       </c>
       <c r="D131">
-        <v>0.8528252145449737</v>
+        <v>0.9999603647982486</v>
       </c>
       <c r="E131">
-        <v>0.1471747854550263</v>
+        <v>3.96352017514312E-05</v>
       </c>
       <c r="F131">
-        <v>0.6471747854550263</v>
+        <v>0.5000396352017514</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3017,10 +3017,10 @@
         <v>130</v>
       </c>
       <c r="B132">
-        <v>1.890962785565988E-08</v>
+        <v>1.222334769600324E-35</v>
       </c>
       <c r="C132">
-        <v>1.890962785565988E-08</v>
+        <v>1.222334769600324E-35</v>
       </c>
       <c r="D132">
         <v>1</v>
